--- a/Files/maharani-panel-chart.xlsx
+++ b/Files/maharani-panel-chart.xlsx
@@ -10,7 +10,7 @@
     <x:sheet name="Source" sheetId="2" r:id="rId3"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$V$280</x:definedName>
+    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$V$282</x:definedName>
   </x:definedNames>
   <x:calcPr calcId="125725"/>
 </x:workbook>
@@ -1883,6 +1883,12 @@
   </x:si>
   <x:si>
     <x:t>31/08/2026 to 06/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07/09/2026 to 13/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14/09/2026 to 20/09/2026</x:t>
   </x:si>
   <x:si>
     <x:t/>
@@ -2341,7 +2347,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:V280"/>
+  <x:dimension ref="A1:V282"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="28.710625" style="0" customWidth="1"/>
@@ -21334,62 +21340,198 @@
         <x:v>219</x:v>
       </x:c>
       <x:c r="E280" s="3" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="F280" s="3" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="G280" s="3" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="H280" s="3" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="I280" s="3" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="J280" s="3" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="K280" s="3" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="L280" s="3" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="M280" s="3" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="N280" s="3" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="O280" s="3" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="P280" s="3" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="Q280" s="3" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="R280" s="3" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="S280" s="3" t="s">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="T280" s="3" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="U280" s="3" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="V280" s="3" t="s">
+        <x:v>192</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="281" spans="1:22">
+      <x:c r="A281" s="3" t="s">
         <x:v>622</x:v>
       </x:c>
-      <x:c r="F280" s="3" t="s">
-        <x:v>622</x:v>
-      </x:c>
-      <x:c r="G280" s="3" t="s">
-        <x:v>622</x:v>
-      </x:c>
-      <x:c r="H280" s="3" t="s">
-        <x:v>622</x:v>
-      </x:c>
-      <x:c r="I280" s="3" t="s">
-        <x:v>622</x:v>
-      </x:c>
-      <x:c r="J280" s="3" t="s">
-        <x:v>622</x:v>
-      </x:c>
-      <x:c r="K280" s="3" t="s">
-        <x:v>622</x:v>
-      </x:c>
-      <x:c r="L280" s="3" t="s">
-        <x:v>622</x:v>
-      </x:c>
-      <x:c r="M280" s="3" t="s">
-        <x:v>622</x:v>
-      </x:c>
-      <x:c r="N280" s="3" t="s">
-        <x:v>622</x:v>
-      </x:c>
-      <x:c r="O280" s="3" t="s">
-        <x:v>622</x:v>
-      </x:c>
-      <x:c r="P280" s="3" t="s">
-        <x:v>622</x:v>
-      </x:c>
-      <x:c r="Q280" s="3" t="s">
-        <x:v>622</x:v>
-      </x:c>
-      <x:c r="R280" s="3" t="s">
-        <x:v>622</x:v>
-      </x:c>
-      <x:c r="S280" s="3" t="s">
-        <x:v>622</x:v>
-      </x:c>
-      <x:c r="T280" s="3" t="s">
-        <x:v>622</x:v>
-      </x:c>
-      <x:c r="U280" s="3" t="s">
-        <x:v>622</x:v>
-      </x:c>
-      <x:c r="V280" s="3" t="s">
-        <x:v>622</x:v>
+      <x:c r="B281" s="3" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="C281" s="3" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="D281" s="3" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="E281" s="3" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="F281" s="3" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="G281" s="3" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="H281" s="3" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="I281" s="3" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="J281" s="3" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K281" s="3" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="L281" s="3" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="M281" s="3" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="N281" s="3" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="O281" s="3" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="P281" s="3" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="Q281" s="3" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="R281" s="3" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="S281" s="3" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="T281" s="3" t="s">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="U281" s="3" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="V281" s="3" t="s">
+        <x:v>114</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="282" spans="1:22">
+      <x:c r="A282" s="3" t="s">
+        <x:v>623</x:v>
+      </x:c>
+      <x:c r="B282" s="3" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="C282" s="3" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="D282" s="3" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="E282" s="3" t="s">
+        <x:v>624</x:v>
+      </x:c>
+      <x:c r="F282" s="3" t="s">
+        <x:v>624</x:v>
+      </x:c>
+      <x:c r="G282" s="3" t="s">
+        <x:v>624</x:v>
+      </x:c>
+      <x:c r="H282" s="3" t="s">
+        <x:v>624</x:v>
+      </x:c>
+      <x:c r="I282" s="3" t="s">
+        <x:v>624</x:v>
+      </x:c>
+      <x:c r="J282" s="3" t="s">
+        <x:v>624</x:v>
+      </x:c>
+      <x:c r="K282" s="3" t="s">
+        <x:v>624</x:v>
+      </x:c>
+      <x:c r="L282" s="3" t="s">
+        <x:v>624</x:v>
+      </x:c>
+      <x:c r="M282" s="3" t="s">
+        <x:v>624</x:v>
+      </x:c>
+      <x:c r="N282" s="3" t="s">
+        <x:v>624</x:v>
+      </x:c>
+      <x:c r="O282" s="3" t="s">
+        <x:v>624</x:v>
+      </x:c>
+      <x:c r="P282" s="3" t="s">
+        <x:v>624</x:v>
+      </x:c>
+      <x:c r="Q282" s="3" t="s">
+        <x:v>624</x:v>
+      </x:c>
+      <x:c r="R282" s="3" t="s">
+        <x:v>624</x:v>
+      </x:c>
+      <x:c r="S282" s="3" t="s">
+        <x:v>624</x:v>
+      </x:c>
+      <x:c r="T282" s="3" t="s">
+        <x:v>624</x:v>
+      </x:c>
+      <x:c r="U282" s="3" t="s">
+        <x:v>624</x:v>
+      </x:c>
+      <x:c r="V282" s="3" t="s">
+        <x:v>624</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:V280"/>
+  <x:autoFilter ref="A1:V282"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
@@ -21412,39 +21554,39 @@
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="4" t="s">
-        <x:v>623</x:v>
+        <x:v>625</x:v>
       </x:c>
       <x:c r="B1" s="4" t="s">
-        <x:v>624</x:v>
+        <x:v>626</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="5" t="s">
-        <x:v>625</x:v>
+        <x:v>627</x:v>
       </x:c>
       <x:c r="B2" s="6" t="s">
-        <x:v>626</x:v>
+        <x:v>628</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="5" t="s">
-        <x:v>627</x:v>
+        <x:v>629</x:v>
       </x:c>
       <x:c r="B3" s="6" t="s">
-        <x:v>628</x:v>
+        <x:v>630</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="5" t="s">
-        <x:v>629</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="B4" s="6">
-        <x:v>279</x:v>
+        <x:v>281</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="5" t="s">
-        <x:v>630</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
         <x:v>22</x:v>
@@ -21452,10 +21594,10 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="5" t="s">
-        <x:v>631</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>621</x:v>
+        <x:v>623</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Files/maharani-panel-chart.xlsx
+++ b/Files/maharani-panel-chart.xlsx
@@ -10,7 +10,7 @@
     <x:sheet name="Source" sheetId="2" r:id="rId3"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$V$282</x:definedName>
+    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$V$283</x:definedName>
   </x:definedNames>
   <x:calcPr calcId="125725"/>
 </x:workbook>
@@ -1889,6 +1889,9 @@
   </x:si>
   <x:si>
     <x:t>14/09/2026 to 20/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21/09/2026 to 27/09/2026</x:t>
   </x:si>
   <x:si>
     <x:t/>
@@ -2347,7 +2350,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:V282"/>
+  <x:dimension ref="A1:V283"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="28.710625" style="0" customWidth="1"/>
@@ -21476,62 +21479,130 @@
         <x:v>169</x:v>
       </x:c>
       <x:c r="E282" s="3" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="F282" s="3" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="G282" s="3" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="H282" s="3" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="I282" s="3" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="J282" s="3" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="K282" s="3" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="L282" s="3" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="M282" s="3" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N282" s="3" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="O282" s="3" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="P282" s="3" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="Q282" s="3" t="s">
+        <x:v>408</x:v>
+      </x:c>
+      <x:c r="R282" s="3" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="S282" s="3" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="T282" s="3" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="U282" s="3" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="V282" s="3" t="s">
+        <x:v>202</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="283" spans="1:22">
+      <x:c r="A283" s="3" t="s">
         <x:v>624</x:v>
       </x:c>
-      <x:c r="F282" s="3" t="s">
-        <x:v>624</x:v>
-      </x:c>
-      <x:c r="G282" s="3" t="s">
-        <x:v>624</x:v>
-      </x:c>
-      <x:c r="H282" s="3" t="s">
-        <x:v>624</x:v>
-      </x:c>
-      <x:c r="I282" s="3" t="s">
-        <x:v>624</x:v>
-      </x:c>
-      <x:c r="J282" s="3" t="s">
-        <x:v>624</x:v>
-      </x:c>
-      <x:c r="K282" s="3" t="s">
-        <x:v>624</x:v>
-      </x:c>
-      <x:c r="L282" s="3" t="s">
-        <x:v>624</x:v>
-      </x:c>
-      <x:c r="M282" s="3" t="s">
-        <x:v>624</x:v>
-      </x:c>
-      <x:c r="N282" s="3" t="s">
-        <x:v>624</x:v>
-      </x:c>
-      <x:c r="O282" s="3" t="s">
-        <x:v>624</x:v>
-      </x:c>
-      <x:c r="P282" s="3" t="s">
-        <x:v>624</x:v>
-      </x:c>
-      <x:c r="Q282" s="3" t="s">
-        <x:v>624</x:v>
-      </x:c>
-      <x:c r="R282" s="3" t="s">
-        <x:v>624</x:v>
-      </x:c>
-      <x:c r="S282" s="3" t="s">
-        <x:v>624</x:v>
-      </x:c>
-      <x:c r="T282" s="3" t="s">
-        <x:v>624</x:v>
-      </x:c>
-      <x:c r="U282" s="3" t="s">
-        <x:v>624</x:v>
-      </x:c>
-      <x:c r="V282" s="3" t="s">
-        <x:v>624</x:v>
+      <x:c r="B283" s="3" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C283" s="3" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="D283" s="3" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="E283" s="3" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F283" s="3" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="G283" s="3" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="H283" s="3" t="s">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="I283" s="3" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="J283" s="3" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="K283" s="3" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="L283" s="3" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="M283" s="3" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="N283" s="3" t="s">
+        <x:v>625</x:v>
+      </x:c>
+      <x:c r="O283" s="3" t="s">
+        <x:v>625</x:v>
+      </x:c>
+      <x:c r="P283" s="3" t="s">
+        <x:v>625</x:v>
+      </x:c>
+      <x:c r="Q283" s="3" t="s">
+        <x:v>625</x:v>
+      </x:c>
+      <x:c r="R283" s="3" t="s">
+        <x:v>625</x:v>
+      </x:c>
+      <x:c r="S283" s="3" t="s">
+        <x:v>625</x:v>
+      </x:c>
+      <x:c r="T283" s="3" t="s">
+        <x:v>625</x:v>
+      </x:c>
+      <x:c r="U283" s="3" t="s">
+        <x:v>625</x:v>
+      </x:c>
+      <x:c r="V283" s="3" t="s">
+        <x:v>625</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:V282"/>
+  <x:autoFilter ref="A1:V283"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
@@ -21554,39 +21625,39 @@
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="4" t="s">
-        <x:v>625</x:v>
+        <x:v>626</x:v>
       </x:c>
       <x:c r="B1" s="4" t="s">
-        <x:v>626</x:v>
+        <x:v>627</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="5" t="s">
-        <x:v>627</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="B2" s="6" t="s">
-        <x:v>628</x:v>
+        <x:v>629</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="5" t="s">
-        <x:v>629</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="B3" s="6" t="s">
-        <x:v>630</x:v>
+        <x:v>631</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="5" t="s">
-        <x:v>631</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="B4" s="6">
-        <x:v>281</x:v>
+        <x:v>282</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="5" t="s">
-        <x:v>632</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
         <x:v>22</x:v>
@@ -21594,10 +21665,10 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="5" t="s">
-        <x:v>633</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>623</x:v>
+        <x:v>624</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
